--- a/artfynd/A 5512-2022 artfynd.xlsx
+++ b/artfynd/A 5512-2022 artfynd.xlsx
@@ -675,53 +675,47 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>98716731</v>
+        <v>98717346</v>
       </c>
       <c r="B2" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Halmstad, Hl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>380048.9898355166</v>
+        <v>380174</v>
       </c>
       <c r="R2" t="n">
-        <v>6285394.922798376</v>
+        <v>6285571</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,19 +745,9 @@
           <t>2022-02-22</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:11</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-02-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,15 +774,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98717346</v>
+        <v>98716731</v>
       </c>
       <c r="B3" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,36 +785,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Halmstad, Hl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>380173.481913586</v>
+        <v>380048</v>
       </c>
       <c r="R3" t="n">
-        <v>6285571.54467013</v>
+        <v>6285395</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +847,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +857,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 5512-2022 artfynd.xlsx
+++ b/artfynd/A 5512-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -771,6 +776,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98717346</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,8 +891,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98716731</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>